--- a/Demo/lf-integrated/demo_lf_itas_9999_4_dbs.xlsx
+++ b/Demo/lf-integrated/demo_lf_itas_9999_4_dbs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\lf-integrated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2A794A-5C88-444B-B7FE-22A190A49009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541D1E63-EA72-4B33-9F1C-36894424D623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -538,9 +538,6 @@
     <t>18 .Le premier résultat du test de ce participant est ${o_result1}. Ce résultat nécessite un deuxième test. Continuez ce questionnaire pour entrer le deuxième résultat du test du participant.</t>
   </si>
   <si>
-    <t>reao_only</t>
-  </si>
-  <si>
     <t>o_recorder</t>
   </si>
   <si>
@@ -598,13 +595,16 @@
     <t>o_id_type</t>
   </si>
   <si>
-    <t>${o_id_type} = 'Io_generation'</t>
-  </si>
-  <si>
     <t>${o_id_type} = 'Scanner'</t>
   </si>
   <si>
-    <t>if(${o_id_type} = 'Io_generation', ${o_code_id1}, if(${o_barcode_method} = 'QRScann', ${o_code_id3}, ${o_code_id5}))</t>
+    <t>${o_id_type} = 'ID_generation'</t>
+  </si>
+  <si>
+    <t>if(${o_id_type} = 'ID_generation', ${o_code_id1}, if(${o_barcode_method} = 'QRScann', ${o_code_id3}, ${o_code_id5}))</t>
+  </si>
+  <si>
+    <t>read_only</t>
   </si>
 </sst>
 </file>
@@ -1332,7 +1332,7 @@
         <v>8</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="O1" s="11" t="s">
         <v>108</v>
@@ -1358,7 +1358,7 @@
         <v>93</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>94</v>
@@ -1390,7 +1390,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>96</v>
@@ -1422,7 +1422,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>98</v>
@@ -1445,7 +1445,7 @@
         <v>99</v>
       </c>
       <c r="Q4" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="R4" s="18"/>
       <c r="S4" s="18"/>
@@ -1456,7 +1456,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>100</v>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="Q5" s="18"/>
       <c r="R5" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="S5" s="18"/>
       <c r="T5" s="18"/>
@@ -1490,7 +1490,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>102</v>
@@ -1515,7 +1515,7 @@
       <c r="Q6" s="18"/>
       <c r="R6" s="18"/>
       <c r="S6" s="18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="T6" s="18"/>
     </row>
@@ -1546,7 +1546,7 @@
         <v>104</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>105</v>
@@ -1576,7 +1576,7 @@
         <v>106</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>107</v>
@@ -1768,7 +1768,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="48" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>115</v>
@@ -1794,7 +1794,7 @@
       <c r="R16" s="18"/>
       <c r="S16" s="18"/>
       <c r="T16" s="49" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:20" s="6" customFormat="1">
@@ -1824,7 +1824,7 @@
         <v>117</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>118</v>
@@ -1834,7 +1834,7 @@
       <c r="F18" s="52"/>
       <c r="G18" s="52"/>
       <c r="H18" s="52" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I18" s="52"/>
       <c r="J18" s="52" t="s">
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="53" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C19" s="53" t="s">
         <v>119</v>
@@ -1866,7 +1866,7 @@
       <c r="F19" s="54"/>
       <c r="G19" s="55"/>
       <c r="H19" s="53" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I19" s="52"/>
       <c r="J19" s="52" t="s">
@@ -1888,7 +1888,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="53" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C20" s="53" t="s">
         <v>120</v>
@@ -1898,7 +1898,7 @@
       <c r="F20" s="54"/>
       <c r="G20" s="55"/>
       <c r="H20" s="53" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I20" s="52"/>
       <c r="J20" s="52" t="s">
@@ -1920,7 +1920,7 @@
         <v>13</v>
       </c>
       <c r="B21" s="53" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C21" s="53" t="s">
         <v>121</v>
@@ -1928,13 +1928,13 @@
       <c r="D21" s="53"/>
       <c r="E21" s="52"/>
       <c r="F21" s="54" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G21" s="55" t="s">
         <v>122</v>
       </c>
       <c r="H21" s="53" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I21" s="52"/>
       <c r="J21" s="52" t="s">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H23" s="57"/>
       <c r="I23" s="56" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J23" s="57" t="s">
         <v>9</v>
@@ -2251,7 +2251,7 @@
       <c r="S31" s="18"/>
       <c r="T31" s="18"/>
     </row>
-    <row r="32" spans="1:20" s="6" customFormat="1" ht="31.5">
+    <row r="32" spans="1:20" s="6" customFormat="1">
       <c r="A32" s="18" t="s">
         <v>60</v>
       </c>
